--- a/Coding Problem List.xlsx
+++ b/Coding Problem List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LearnHub\DevSkill\Laravel\Problem Solving - PHP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20EBADB-82E4-47B2-ABD0-EFC35B8AFC34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D605ADC2-EB1D-4111-A012-1E72EEEB5E43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="77">
   <si>
     <t>Problems</t>
   </si>
@@ -291,7 +291,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,7 +318,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -346,7 +352,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,7 +615,7 @@
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="11">
         <v>1</v>
       </c>
     </row>
@@ -623,7 +631,7 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="9">
         <v>1</v>
       </c>
     </row>
@@ -647,7 +655,7 @@
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="12">
         <v>1</v>
       </c>
     </row>
@@ -671,7 +679,7 @@
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="10">
         <v>1</v>
       </c>
     </row>
@@ -791,7 +799,7 @@
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="8">
         <v>1</v>
       </c>
     </row>

--- a/Coding Problem List.xlsx
+++ b/Coding Problem List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LearnHub\DevSkill\Laravel\Problem Solving - PHP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D605ADC2-EB1D-4111-A012-1E72EEEB5E43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CAAB01-8277-4756-860C-A6BA6ACFECFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
   <si>
     <t>Problems</t>
   </si>
@@ -807,7 +807,7 @@
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="8">
         <v>1</v>
       </c>
     </row>
@@ -815,7 +815,7 @@
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="8">
         <v>1</v>
       </c>
     </row>
@@ -919,7 +919,7 @@
       <c r="A40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="8">
         <v>1</v>
       </c>
     </row>

--- a/Coding Problem List.xlsx
+++ b/Coding Problem List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LearnHub\DevSkill\Laravel\Problem Solving - PHP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CAAB01-8277-4756-860C-A6BA6ACFECFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A4D4C0-2C2A-468C-B9CF-5C77A36B7FD3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="77">
   <si>
     <t>Problems</t>
   </si>
@@ -623,7 +623,7 @@
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
     </row>
